--- a/booking_forms/032_performance_evaluation_slot_booking_form--booking_forms.xlsx
+++ b/booking_forms/032_performance_evaluation_slot_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reviewee</t>
+          <t>Reviewee Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reviewee</t>
+          <t>Reviewee Email</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>reviewee</t>
+          <t>reviewee_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reviewee</t>
+          <t>Reviewee 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>slot_duration</t>
+          <t>slot_duration_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slot Duration</t>
+          <t>Slot Duration 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>slot_frequency</t>
+          <t>slot_frequency_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slot Frequency</t>
+          <t>Slot Frequency 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'manager_3'}</t>
+          <t>manager_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Manager 3'}</t>
+          <t>Manager 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'reviewee_1'}</t>
+          <t>reviewee_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Reviewee 1'}</t>
+          <t>Reviewee 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reviewee_2'}</t>
+          <t>reviewee_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reviewee 2'}</t>
+          <t>Reviewee 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1234567890}</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1234567890}</t>
+          <t>1234567890</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_9876543210}</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 9876543210}</t>
+          <t>9876543210</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1234567890}</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1234567890}</t>
+          <t>1234567890</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_9876543210}</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 9876543210}</t>
+          <t>9876543210</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email1@example.com'}</t>
+          <t>email1@example.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'email1@example.com'}</t>
+          <t>email1@example.com</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email2@example.com'}</t>
+          <t>email2@example.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'email2@example.com'}</t>
+          <t>email2@example.com</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email1@example.com'}</t>
+          <t>email1@example.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'email1@example.com'}</t>
+          <t>email1@example.com</t>
         </is>
       </c>
     </row>
@@ -1488,165 +1488,165 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email2@example.com'}</t>
+          <t>email2@example.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'email2@example.com'}</t>
+          <t>email2@example.com</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>manager_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>manager_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>reviewee_choices</t>
+          <t>reviewee_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'reviewee_1'}</t>
+          <t>reviewee_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Reviewee 1'}</t>
+          <t>Reviewee 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>reviewee_choices</t>
+          <t>reviewee_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reviewee_2'}</t>
+          <t>reviewee_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reviewee 2'}</t>
+          <t>Reviewee 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>slot_duration_choices</t>
+          <t>slot_duration_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>slot_duration_choices</t>
+          <t>slot_duration_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>slot_frequency_choices</t>
+          <t>slot_frequency_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>slot_frequency_choices</t>
+          <t>slot_frequency_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>slot_frequency_choices</t>
+          <t>slot_frequency_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
